--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40522-2026 artfynd.xlsx
+++ b/artfynd/A 40522-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136949721</v>
       </c>
       <c r="B3" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
